--- a/rules/Card Manifest.xlsx
+++ b/rules/Card Manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\States of Siege Diriyah\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086EC5F9-DA0E-4B06-B1F6-7AE228D6751F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADEBE7B-4E5A-436B-ADC0-FC665F0447E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="200">
   <si>
     <t>Card Number</t>
   </si>
@@ -124,9 +124,6 @@
     <t>ADVANCE</t>
   </si>
   <si>
-    <t>MINING &amp; TUNNELING</t>
-  </si>
-  <si>
     <t>PASHA</t>
   </si>
   <si>
@@ -145,9 +142,6 @@
     <t>REINFORCEMENTS</t>
   </si>
   <si>
-    <t>Reconnaisance</t>
-  </si>
-  <si>
     <t>Cavalry</t>
   </si>
   <si>
@@ -454,33 +448,15 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Elite Cavalry</t>
-  </si>
-  <si>
     <t>Add Elite Cavalry to S Fronts</t>
   </si>
   <si>
-    <t>Tunnels</t>
-  </si>
-  <si>
     <t>2 Tunneling to Siege Camp</t>
   </si>
   <si>
-    <t>Mining</t>
-  </si>
-  <si>
     <t>2 Mining to Siege Camp</t>
   </si>
   <si>
-    <t>Local Traitors</t>
-  </si>
-  <si>
-    <t>Tactical Flanking</t>
-  </si>
-  <si>
-    <t>Tactical Flanking marker NE; no Wahhabi Actions</t>
-  </si>
-  <si>
     <t>3 (1 if Supply Disrupted)</t>
   </si>
   <si>
@@ -493,48 +469,24 @@
     <t>2 Mining markers to Siege Camp</t>
   </si>
   <si>
-    <t>Reinforcements</t>
-  </si>
-  <si>
     <t>Add 1 Artillery, 1 Cavalry to Siege Camp</t>
   </si>
   <si>
-    <t>Night Ambush</t>
-  </si>
-  <si>
     <t>Ambush markers to W, NE Fronts</t>
   </si>
   <si>
-    <t>Uzun Ali</t>
-  </si>
-  <si>
-    <t>Bedouin Tribes</t>
-  </si>
-  <si>
     <t>-2 Wahhabi Morale</t>
   </si>
   <si>
-    <t>Al Maghariba Diversion</t>
-  </si>
-  <si>
     <t>No Wahhabi Events or Actions this turn</t>
   </si>
   <si>
-    <t>Counter-Battery</t>
-  </si>
-  <si>
     <t>Remove one Wahhabi Artillery Unit</t>
   </si>
   <si>
-    <t>Bedouin Supply Protection</t>
-  </si>
-  <si>
     <t>Supply Status to NORMAL</t>
   </si>
   <si>
-    <t>Cavalry Sweep</t>
-  </si>
-  <si>
     <t>Move Cavalry Units to Western Front</t>
   </si>
   <si>
@@ -553,60 +505,27 @@
     <t>Uzun Ali to Supply Lines</t>
   </si>
   <si>
-    <t>Citadel Famine</t>
-  </si>
-  <si>
-    <t>-2 Wahhabi Supply</t>
-  </si>
-  <si>
-    <t>Tactical Flanking marker W; no Wahhabi Actions</t>
-  </si>
-  <si>
-    <t>Rally</t>
-  </si>
-  <si>
     <t>Flip All Units from Disrupted to Full Strength</t>
   </si>
   <si>
     <t>Sickness &amp; Heatstroke</t>
   </si>
   <si>
-    <t>Siege Famine</t>
-  </si>
-  <si>
-    <t>Tactical Flanking marker NE</t>
-  </si>
-  <si>
-    <t>Tactical Flanking marker W</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>1M, 3T</t>
-  </si>
-  <si>
-    <t>2T, 2M</t>
-  </si>
-  <si>
     <t>1T</t>
   </si>
   <si>
     <t>OTHER IDEAS</t>
   </si>
   <si>
-    <t>Vaissière - French Engineer</t>
-  </si>
-  <si>
     <t>Redeploy 1 artillery, 1 cavalry from siege camp to random front</t>
   </si>
   <si>
     <t>Redeployment  (x2?)</t>
   </si>
   <si>
-    <t>Khalil Pasha - Reinforcements</t>
-  </si>
-  <si>
     <t>Rashwan Agha</t>
   </si>
   <si>
@@ -617,13 +536,112 @@
   </si>
   <si>
     <t>Causes Two Breaches to Front Line Stronghold</t>
+  </si>
+  <si>
+    <t>FASTEST</t>
+  </si>
+  <si>
+    <t>SLOWEST</t>
+  </si>
+  <si>
+    <t>Vaissière</t>
+  </si>
+  <si>
+    <t>VAISSIERE</t>
+  </si>
+  <si>
+    <t>REDEPLOYMENT</t>
+  </si>
+  <si>
+    <t>-2 Wahhabi Supply; no Wahhabi Actions this turn</t>
+  </si>
+  <si>
+    <t>Redeploy 1 artillery, 1 cavalry from siege camp to fastest advance</t>
+  </si>
+  <si>
+    <t>Redeploy 1 artillery, 1 cavalry from siege camp to slowest advance</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>TACTICAL FLANKING (F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINING (M), </t>
+  </si>
+  <si>
+    <t>TUNNELING (T) &amp;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Y</t>
+  </si>
+  <si>
+    <t>1M, 3T, 2F</t>
+  </si>
+  <si>
+    <t>2T, 2M, 2F</t>
+  </si>
+  <si>
+    <t>RASHWAN AGHA</t>
+  </si>
+  <si>
+    <t>+2 to all combats on NE FRONT</t>
+  </si>
+  <si>
+    <t>RECONNAISANCE</t>
+  </si>
+  <si>
+    <t>ARTILLERY</t>
+  </si>
+  <si>
+    <t>ELITE CAVALRY</t>
+  </si>
+  <si>
+    <t>TUNNELS</t>
+  </si>
+  <si>
+    <t>LOCAL TRAITORS</t>
+  </si>
+  <si>
+    <t>MINING</t>
+  </si>
+  <si>
+    <t>NIGHT AMBUSH</t>
+  </si>
+  <si>
+    <t>UZUN ALI</t>
+  </si>
+  <si>
+    <t>BEDOUIN TRIBES</t>
+  </si>
+  <si>
+    <t>AL MAGHARIBA DIVERSION</t>
+  </si>
+  <si>
+    <t>COUNTER-BATTERY</t>
+  </si>
+  <si>
+    <t>BEDOUIN SUPPLY PROTECTION</t>
+  </si>
+  <si>
+    <t>CAVALRY SWEEP</t>
+  </si>
+  <si>
+    <t>CITADEL FAMINE</t>
+  </si>
+  <si>
+    <t>RALLY</t>
+  </si>
+  <si>
+    <t>SIEGE FAMINE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,6 +698,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1229,7 +1255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1432,14 +1458,10 @@
     <xf numFmtId="49" fontId="3" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1473,6 +1495,21 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1796,13 +1833,13 @@
     <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="67.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="69.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.08984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="36.90625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.08984375" bestFit="1" customWidth="1"/>
@@ -1816,29 +1853,33 @@
         <v>1</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G1" s="3"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="5" t="s">
+      <c r="H1" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1" s="69" t="s">
+        <v>176</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="69"/>
-      <c r="K1" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="M1" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N1" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -1846,30 +1887,30 @@
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
       <c r="E2" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>34</v>
-      </c>
       <c r="H2" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="J2" s="74" t="s">
         <v>33</v>
-      </c>
-      <c r="J2" s="74" t="s">
-        <v>34</v>
       </c>
       <c r="K2" s="13"/>
       <c r="L2" s="10"/>
       <c r="M2" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
@@ -1880,10 +1921,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>36</v>
+        <v>184</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>6</v>
@@ -1892,7 +1933,7 @@
         <v>6</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>6</v>
@@ -1905,7 +1946,7 @@
       </c>
       <c r="K3" s="61"/>
       <c r="L3" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M3" s="66">
         <v>1</v>
@@ -1919,25 +1960,25 @@
         <v>2</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="J4" s="76" t="s">
         <v>6</v>
@@ -1946,13 +1987,13 @@
         <v>6</v>
       </c>
       <c r="L4" s="26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M4" s="63" t="s">
         <v>6</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -1960,25 +2001,25 @@
         <v>3</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G5" s="70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H5" s="71" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="J5" s="76" t="s">
         <v>6</v>
@@ -1987,13 +2028,13 @@
         <v>6</v>
       </c>
       <c r="L5" s="26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M5" s="63" t="s">
         <v>6</v>
       </c>
       <c r="N5" s="27" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -2001,19 +2042,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G6" s="70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H6" s="71" t="s">
         <v>6</v>
@@ -2026,11 +2067,11 @@
       </c>
       <c r="K6" s="28"/>
       <c r="L6" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M6" s="63"/>
       <c r="N6" s="27" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -2038,16 +2079,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G7" s="70"/>
       <c r="H7" s="71" t="s">
@@ -2069,15 +2110,15 @@
         <v>2</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="25"/>
@@ -2096,16 +2137,16 @@
         <v>3</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G9" s="70"/>
       <c r="H9" s="71" t="s">
@@ -2116,7 +2157,7 @@
       </c>
       <c r="J9" s="76"/>
       <c r="K9" s="28" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L9" s="26"/>
       <c r="M9" s="63"/>
@@ -2127,16 +2168,16 @@
         <v>4</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G10" s="70"/>
       <c r="H10" s="71" t="s">
@@ -2147,7 +2188,7 @@
       </c>
       <c r="J10" s="76"/>
       <c r="K10" s="28" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L10" s="26"/>
       <c r="M10" s="63"/>
@@ -2158,20 +2199,20 @@
         <v>5</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="25"/>
       <c r="J11" s="76" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="K11" s="28" t="s">
         <v>6</v>
@@ -2184,22 +2225,22 @@
       <c r="B12" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>147</v>
+      <c r="C12" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="97" t="s">
+        <v>166</v>
       </c>
       <c r="E12" s="25"/>
       <c r="F12" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G12" s="70" t="s">
         <v>6</v>
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="25" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="J12" s="76" t="s">
         <v>6</v>
@@ -2208,26 +2249,26 @@
         <v>6</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M12" s="63"/>
       <c r="N12" s="27"/>
     </row>
-    <row r="13" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B13" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>151</v>
-      </c>
       <c r="E13" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>138</v>
+        <v>6</v>
+      </c>
+      <c r="F13" s="96" t="s">
+        <v>167</v>
       </c>
       <c r="G13" s="70"/>
       <c r="H13" s="71" t="s">
@@ -2238,27 +2279,27 @@
       </c>
       <c r="J13" s="76"/>
       <c r="K13" s="28" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="L13" s="26"/>
       <c r="M13" s="63"/>
       <c r="N13" s="27"/>
     </row>
-    <row r="14" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B14" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>151</v>
-      </c>
       <c r="E14" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>138</v>
+        <v>6</v>
+      </c>
+      <c r="F14" s="96" t="s">
+        <v>168</v>
       </c>
       <c r="G14" s="70"/>
       <c r="H14" s="71" t="s">
@@ -2269,7 +2310,7 @@
       </c>
       <c r="J14" s="76"/>
       <c r="K14" s="28" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="L14" s="26"/>
       <c r="M14" s="63"/>
@@ -2280,15 +2321,15 @@
         <v>10</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
       <c r="G15" s="70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H15" s="71"/>
       <c r="I15" s="25"/>
@@ -2298,10 +2339,10 @@
       <c r="K15" s="28"/>
       <c r="L15" s="26"/>
       <c r="M15" s="68" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="N15" s="68" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -2309,10 +2350,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>189</v>
+        <v>34</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E16" s="25"/>
       <c r="F16" s="25"/>
@@ -2327,10 +2368,10 @@
       <c r="K16" s="28"/>
       <c r="L16" s="26"/>
       <c r="M16" s="68" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="N16" s="68" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -2338,23 +2379,23 @@
         <v>11</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G17" s="70"/>
       <c r="H17" s="71" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="J17" s="76"/>
       <c r="K17" s="28" t="s">
@@ -2369,10 +2410,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
@@ -2381,7 +2422,7 @@
       <c r="I18" s="25"/>
       <c r="J18" s="76"/>
       <c r="K18" s="77" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="L18" s="26"/>
       <c r="M18" s="63"/>
@@ -2392,20 +2433,20 @@
         <v>14</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="D19" s="67" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G19" s="70"/>
       <c r="H19" s="71" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="I19" s="25" t="s">
         <v>6</v>
@@ -2423,16 +2464,16 @@
         <v>15</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G20" s="70"/>
       <c r="H20" s="71" t="s">
@@ -2452,14 +2493,14 @@
         <v>16</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="E21" s="25"/>
       <c r="F21" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G21" s="70"/>
       <c r="H21" s="71"/>
@@ -2477,14 +2518,14 @@
         <v>17</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E22" s="25"/>
       <c r="F22" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G22" s="70"/>
       <c r="H22" s="71"/>
@@ -2502,13 +2543,13 @@
         <v>19</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F23" s="25"/>
       <c r="G23" s="70"/>
@@ -2519,34 +2560,40 @@
       <c r="J23" s="76"/>
       <c r="K23" s="28"/>
       <c r="L23" s="26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M23" s="63"/>
       <c r="N23" s="27"/>
     </row>
-    <row r="24" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B24" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>174</v>
+        <v>171</v>
+      </c>
+      <c r="D24" s="98" t="s">
+        <v>173</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" s="25"/>
+        <v>136</v>
+      </c>
+      <c r="F24" s="96" t="s">
+        <v>6</v>
+      </c>
       <c r="G24" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H24" s="71"/>
-      <c r="I24" s="25"/>
+      <c r="H24" s="71" t="s">
+        <v>175</v>
+      </c>
+      <c r="I24" s="25" t="s">
+        <v>6</v>
+      </c>
       <c r="J24" s="76"/>
       <c r="K24" s="28"/>
       <c r="L24" s="26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M24" s="63"/>
       <c r="N24" s="27"/>
@@ -2556,15 +2603,15 @@
         <v>20</v>
       </c>
       <c r="C25" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="D25" s="67" t="s">
         <v>172</v>
-      </c>
-      <c r="D25" s="67" t="s">
-        <v>173</v>
       </c>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
       <c r="G25" s="70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H25" s="71"/>
       <c r="I25" s="25"/>
@@ -2579,16 +2626,16 @@
         <v>21</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>176</v>
+        <v>198</v>
+      </c>
+      <c r="D26" s="99" t="s">
+        <v>156</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G26" s="70"/>
       <c r="H26" s="71"/>
@@ -2596,7 +2643,7 @@
       <c r="J26" s="76"/>
       <c r="K26" s="28"/>
       <c r="L26" s="26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M26" s="63"/>
       <c r="N26" s="27"/>
@@ -2606,16 +2653,16 @@
         <v>22</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G27" s="70"/>
       <c r="H27" s="71"/>
@@ -2623,7 +2670,7 @@
       <c r="J27" s="76"/>
       <c r="K27" s="28"/>
       <c r="L27" s="26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M27" s="63"/>
       <c r="N27" s="27"/>
@@ -2633,16 +2680,16 @@
         <v>23</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G28" s="70"/>
       <c r="H28" s="71"/>
@@ -2650,7 +2697,7 @@
       <c r="J28" s="76"/>
       <c r="K28" s="28"/>
       <c r="L28" s="26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M28" s="63"/>
       <c r="N28" s="27"/>
@@ -2660,16 +2707,16 @@
         <v>25</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="D29" s="67" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G29" s="32" t="s">
         <v>6</v>
@@ -2678,7 +2725,7 @@
         <v>6</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="J29" s="33"/>
       <c r="K29" s="73"/>
@@ -2691,15 +2738,15 @@
         <v>24</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="D30" s="67" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E30" s="31"/>
       <c r="F30" s="31"/>
       <c r="G30" s="70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H30" s="71" t="s">
         <v>6</v>
@@ -2716,22 +2763,26 @@
         <v>26</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="98" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" s="31"/>
+      <c r="F31" s="65" t="s">
         <v>179</v>
-      </c>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31" t="s">
-        <v>138</v>
       </c>
       <c r="G31" s="32"/>
       <c r="H31" s="72"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="33"/>
+      <c r="I31" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" s="33" t="s">
+        <v>6</v>
+      </c>
       <c r="K31" s="73"/>
       <c r="L31" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M31" s="63"/>
       <c r="N31" s="27"/>
@@ -2740,63 +2791,65 @@
       <c r="B32" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="93" t="s">
-        <v>146</v>
-      </c>
-      <c r="D32" s="80" t="s">
-        <v>180</v>
-      </c>
-      <c r="E32" s="81" t="s">
-        <v>138</v>
-      </c>
-      <c r="F32" s="81"/>
-      <c r="G32" s="82"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="84"/>
-      <c r="K32" s="84"/>
-      <c r="L32" s="85" t="s">
-        <v>135</v>
-      </c>
-      <c r="M32" s="86"/>
-      <c r="N32" s="87"/>
+      <c r="C32" s="91" t="s">
+        <v>182</v>
+      </c>
+      <c r="D32" s="100" t="s">
+        <v>183</v>
+      </c>
+      <c r="E32" s="80" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="80"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32" s="80"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="83" t="s">
+        <v>133</v>
+      </c>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
     </row>
     <row r="33" spans="2:14" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="88" t="s">
-        <v>181</v>
-      </c>
-      <c r="C33" s="89"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90">
+      <c r="B33" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" s="87"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88">
         <f>COUNTIF(E3:E32, "Y")</f>
-        <v>18</v>
-      </c>
-      <c r="F33" s="90">
+        <v>16</v>
+      </c>
+      <c r="F33" s="88">
         <f>COUNTIF(F3:F32, "Y")</f>
-        <v>19</v>
-      </c>
-      <c r="G33" s="90">
+        <v>16</v>
+      </c>
+      <c r="G33" s="88">
         <f>COUNTIF(G3:G32, "Y")</f>
         <v>9</v>
       </c>
-      <c r="H33" s="90" t="s">
-        <v>182</v>
-      </c>
-      <c r="I33" s="90" t="s">
-        <v>183</v>
-      </c>
-      <c r="J33" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="K33" s="90" t="s">
-        <v>6</v>
-      </c>
-      <c r="L33" s="91">
+      <c r="H33" s="88" t="s">
+        <v>180</v>
+      </c>
+      <c r="I33" s="88" t="s">
+        <v>181</v>
+      </c>
+      <c r="J33" s="88" t="s">
+        <v>159</v>
+      </c>
+      <c r="K33" s="88" t="s">
+        <v>6</v>
+      </c>
+      <c r="L33" s="89">
         <f>COUNTA(L3:L32)</f>
         <v>12</v>
       </c>
-      <c r="M33" s="92"/>
-      <c r="N33" s="94"/>
+      <c r="M33" s="90"/>
+      <c r="N33" s="92"/>
     </row>
     <row r="34" spans="2:14" ht="19" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B34" s="1"/>
@@ -2809,13 +2862,13 @@
     </row>
     <row r="35" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B35" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C35" s="96" t="s">
-        <v>186</v>
+        <v>160</v>
+      </c>
+      <c r="C35" s="94" t="s">
+        <v>169</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="E35" s="62"/>
       <c r="F35" s="62"/>
@@ -2825,22 +2878,22 @@
       <c r="J35" s="6"/>
     </row>
     <row r="36" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="C36" s="95" t="s">
-        <v>188</v>
+      <c r="C36" s="93" t="s">
+        <v>162</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="E36" s="56"/>
       <c r="F36" s="56"/>
       <c r="G36" s="56"/>
     </row>
     <row r="37" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="C37" s="95" t="s">
-        <v>190</v>
-      </c>
-      <c r="D37" s="97" t="s">
-        <v>192</v>
+      <c r="C37" s="93" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" s="95" t="s">
+        <v>165</v>
       </c>
       <c r="E37" s="56"/>
       <c r="F37" s="56"/>
@@ -2894,16 +2947,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -2911,152 +2964,152 @@
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
       <c r="E2" s="36" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F2" s="10"/>
       <c r="G2" s="55" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="19" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B3" s="57" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E3" s="52">
         <v>2</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="53" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B4" s="58" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E4" s="42">
         <v>3</v>
       </c>
       <c r="F4" s="40"/>
       <c r="G4" s="41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B5" s="58" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5" s="42">
         <v>3</v>
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B6" s="58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E6" s="42">
         <v>3</v>
       </c>
       <c r="F6" s="40"/>
       <c r="G6" s="41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B7" s="58" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C7" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="39" t="s">
         <v>82</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>84</v>
       </c>
       <c r="E7" s="42">
         <v>2</v>
       </c>
       <c r="F7" s="40"/>
       <c r="G7" s="54" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B8" s="58" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8" s="42">
         <v>2</v>
       </c>
       <c r="F8" s="40"/>
       <c r="G8" s="41" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B9" s="58" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" s="42">
         <v>1</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G9" s="54" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B10" s="58" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E10" s="42">
         <v>3</v>
@@ -3066,13 +3119,13 @@
     </row>
     <row r="11" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B11" s="58" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E11" s="42">
         <v>3</v>
@@ -3082,13 +3135,13 @@
     </row>
     <row r="12" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B12" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E12" s="42">
         <v>1</v>
@@ -3098,107 +3151,107 @@
     </row>
     <row r="13" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B13" s="58" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E13" s="42">
         <v>1</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B14" s="58" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C14" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="39" t="s">
         <v>95</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>97</v>
       </c>
       <c r="E14" s="42">
         <v>1</v>
       </c>
       <c r="F14" s="40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B15" s="58" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C15" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="39" t="s">
         <v>95</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>97</v>
       </c>
       <c r="E15" s="42">
         <v>1</v>
       </c>
       <c r="F15" s="40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B16" s="58" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E16" s="42">
         <v>1</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B17" s="58" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E17" s="42">
         <v>1</v>
       </c>
       <c r="F17" s="40"/>
       <c r="G17" s="41" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B18" s="58" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E18" s="42">
         <v>2</v>
@@ -3211,100 +3264,100 @@
         <v>47</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E19" s="42">
         <v>2</v>
       </c>
       <c r="F19" s="40"/>
       <c r="G19" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B20" s="58" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E20" s="42">
         <v>1</v>
       </c>
       <c r="F20" s="40"/>
       <c r="G20" s="41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B21" s="58" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E21" s="42">
         <v>1</v>
       </c>
       <c r="F21" s="40"/>
       <c r="G21" s="41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B22" s="58" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E22" s="42">
         <v>2</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B23" s="58" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E23" s="42">
         <v>2</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="54" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B24" s="58" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E24" s="42">
         <v>2</v>
@@ -3314,13 +3367,13 @@
     </row>
     <row r="25" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B25" s="58" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E25" s="42">
         <v>2</v>
@@ -3330,13 +3383,13 @@
     </row>
     <row r="26" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B26" s="58" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E26" s="42">
         <v>3</v>
@@ -3346,49 +3399,49 @@
     </row>
     <row r="27" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B27" s="59" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E27" s="44">
         <v>1</v>
       </c>
       <c r="F27" s="45"/>
       <c r="G27" s="41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B28" s="59" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E28" s="44">
         <v>1</v>
       </c>
       <c r="F28" s="45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G28" s="41"/>
     </row>
     <row r="29" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B29" s="59" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E29" s="44">
         <v>2</v>
@@ -3398,13 +3451,13 @@
     </row>
     <row r="30" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B30" s="59" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E30" s="44">
         <v>3</v>
@@ -3414,37 +3467,37 @@
     </row>
     <row r="31" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B31" s="59" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C31" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="39" t="s">
         <v>127</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>129</v>
       </c>
       <c r="E31" s="42">
         <v>3</v>
       </c>
       <c r="F31" s="40"/>
       <c r="G31" s="54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="19" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B32" s="60" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D32" s="48" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E32" s="49">
         <v>4</v>
       </c>
       <c r="F32" s="50" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G32" s="51"/>
     </row>

--- a/rules/Card Manifest.xlsx
+++ b/rules/Card Manifest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\States of Siege Diriyah\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADEBE7B-4E5A-436B-ADC0-FC665F0447E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9582C6BF-9963-43D7-B861-575EB6DE7EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="193">
   <si>
     <t>Card Number</t>
   </si>
@@ -310,9 +310,6 @@
     <t>Horse Starvation</t>
   </si>
   <si>
-    <t>Remove 1 Ottoman Cavalry Unit from the map</t>
-  </si>
-  <si>
     <t>Place 2 Barricades markers to Settlements/Wadi spaces</t>
   </si>
   <si>
@@ -343,9 +340,6 @@
     <t>Palm Grove Harvest</t>
   </si>
   <si>
-    <t>NE FRONT is Disrupted; W Front is N already Disrupted</t>
-  </si>
-  <si>
     <t>Barricades</t>
   </si>
   <si>
@@ -358,21 +352,9 @@
     <t>2 x TRENCHES (+1 Defense)</t>
   </si>
   <si>
-    <t>Place Tower Outposes marker on Ottoman Front</t>
-  </si>
-  <si>
     <t>1 x TOWER OUTPOST (-1 Ottoman Attack)</t>
   </si>
   <si>
-    <t>Tower Outposts</t>
-  </si>
-  <si>
-    <t>Counter-Tunneling</t>
-  </si>
-  <si>
-    <t>2 x COUNTER-TUNNELING</t>
-  </si>
-  <si>
     <t>Breach Repairs</t>
   </si>
   <si>
@@ -412,18 +394,6 @@
     <t>Flip All Ottoman Fronts to Disrupted</t>
   </si>
   <si>
-    <t>Counter-Mining</t>
-  </si>
-  <si>
-    <t>Place 2 Counter-Tunneling markers in Reserve</t>
-  </si>
-  <si>
-    <t>Place 2 Counter-Mining markers in Reserve</t>
-  </si>
-  <si>
-    <t>2 x COUNTER-MINING</t>
-  </si>
-  <si>
     <t>Explosion in Siege Camp</t>
   </si>
   <si>
@@ -442,39 +412,15 @@
     <t>Add Artillery Unit to All 3 Fronts</t>
   </si>
   <si>
-    <t>Add Elite Cavalry to W and NE Fronts</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>Add Elite Cavalry to S Fronts</t>
-  </si>
-  <si>
-    <t>2 Tunneling to Siege Camp</t>
-  </si>
-  <si>
-    <t>2 Mining to Siege Camp</t>
-  </si>
-  <si>
-    <t>3 (1 if Supply Disrupted)</t>
-  </si>
-  <si>
     <t>Place Local Traitors marker on S Front Wahhabi Space</t>
   </si>
   <si>
-    <t>2 Tunneling markers to Siege Camp</t>
-  </si>
-  <si>
-    <t>2 Mining markers to Siege Camp</t>
-  </si>
-  <si>
     <t>Add 1 Artillery, 1 Cavalry to Siege Camp</t>
   </si>
   <si>
-    <t>Ambush markers to W, NE Fronts</t>
-  </si>
-  <si>
     <t>-2 Wahhabi Morale</t>
   </si>
   <si>
@@ -493,12 +439,6 @@
     <t>1 to Siege Camp</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>MARKERS</t>
   </si>
   <si>
@@ -514,27 +454,9 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>1T</t>
-  </si>
-  <si>
-    <t>OTHER IDEAS</t>
-  </si>
-  <si>
-    <t>Redeploy 1 artillery, 1 cavalry from siege camp to random front</t>
-  </si>
-  <si>
-    <t>Redeployment  (x2?)</t>
-  </si>
-  <si>
-    <t>Rashwan Agha</t>
-  </si>
-  <si>
     <t>Uzun Ali marker to Supply Lines box; +2 to all attacks</t>
   </si>
   <si>
-    <t>+2 to all attacks on NE FRONT</t>
-  </si>
-  <si>
     <t>Causes Two Breaches to Front Line Stronghold</t>
   </si>
   <si>
@@ -544,9 +466,6 @@
     <t>SLOWEST</t>
   </si>
   <si>
-    <t>Vaissière</t>
-  </si>
-  <si>
     <t>VAISSIERE</t>
   </si>
   <si>
@@ -556,24 +475,9 @@
     <t>-2 Wahhabi Supply; no Wahhabi Actions this turn</t>
   </si>
   <si>
-    <t>Redeploy 1 artillery, 1 cavalry from siege camp to fastest advance</t>
-  </si>
-  <si>
-    <t>Redeploy 1 artillery, 1 cavalry from siege camp to slowest advance</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
-    <t>TACTICAL FLANKING (F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MINING (M), </t>
-  </si>
-  <si>
-    <t>TUNNELING (T) &amp;</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Y</t>
   </si>
   <si>
@@ -598,18 +502,9 @@
     <t>ELITE CAVALRY</t>
   </si>
   <si>
-    <t>TUNNELS</t>
-  </si>
-  <si>
     <t>LOCAL TRAITORS</t>
   </si>
   <si>
-    <t>MINING</t>
-  </si>
-  <si>
-    <t>NIGHT AMBUSH</t>
-  </si>
-  <si>
     <t>UZUN ALI</t>
   </si>
   <si>
@@ -635,13 +530,97 @@
   </si>
   <si>
     <t>SIEGE FAMINE</t>
+  </si>
+  <si>
+    <t>KHALIL PASHA REINFORCEMENTS</t>
+  </si>
+  <si>
+    <t>Local Traitors Marker SOUTHERN</t>
+  </si>
+  <si>
+    <t>Ambush Markers all Fronts</t>
+  </si>
+  <si>
+    <t>1 toW</t>
+  </si>
+  <si>
+    <t>1 to NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 to S </t>
+  </si>
+  <si>
+    <t>Redeploy 2 artillery, 2 cavalry from siege camp to fastest advance</t>
+  </si>
+  <si>
+    <t>Redeploy 2 artillery, 2 cavalry from siege camp to slowest advance</t>
+  </si>
+  <si>
+    <t>-1 Wahhabi Supply; no Wahhabi Actions this turn</t>
+  </si>
+  <si>
+    <t>Add Elite Cavalry to W and NE Fronts unless outnumbered in Supply Lines</t>
+  </si>
+  <si>
+    <t>Add Elite Cavalry to S Fronts unless outnumbered in Supply Lines</t>
+  </si>
+  <si>
+    <t>RAPID ADVANCE</t>
+  </si>
+  <si>
+    <t>Automatic advance into the next Settlement, Wadi or Heights space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TACTICAL </t>
+  </si>
+  <si>
+    <t>FLANKING</t>
+  </si>
+  <si>
+    <t>SUPPLY ROUTE SHIFTED</t>
+  </si>
+  <si>
+    <t>All Units in Suppy Lines Attackers box to Reserve</t>
+  </si>
+  <si>
+    <t>CAVALRY DESERTION</t>
+  </si>
+  <si>
+    <t>Remove one Wahhabi Khayala Unit</t>
+  </si>
+  <si>
+    <t>Cavalry Dispersed</t>
+  </si>
+  <si>
+    <t>Return 2 Cavalry Units from Western Front to Siege Camp</t>
+  </si>
+  <si>
+    <t>Ammunition Shortage</t>
+  </si>
+  <si>
+    <t>Return 2 Artillery Units to Siege Camp</t>
+  </si>
+  <si>
+    <t>Flip All Ottoman Artillery Units to Disrupted (SAUDI INITIATIVE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove 2 Ottoman Artillery Units  </t>
+  </si>
+  <si>
+    <t>Artillery Attrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove 2 Ottoman Cavalry Units  </t>
+  </si>
+  <si>
+    <t>ARTILLERY ATTRITION</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -706,6 +685,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -757,7 +744,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -926,21 +913,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -1117,32 +1089,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color auto="1"/>
       </left>
@@ -1191,8 +1137,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1200,49 +1150,105 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="thick">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thick">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top style="thick">
         <color auto="1"/>
       </top>
@@ -1255,7 +1261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1272,39 +1278,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1333,20 +1339,17 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1369,21 +1372,21 @@
     <xf numFmtId="49" fontId="3" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1393,7 +1396,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1402,10 +1405,10 @@
     <xf numFmtId="1" fontId="3" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1420,97 +1423,124 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1827,25 +1857,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.1796875" customWidth="1"/>
     <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="69.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:13" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1860,29 +1889,26 @@
         <v>28</v>
       </c>
       <c r="G1" s="3"/>
-      <c r="H1" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="I1" s="12" t="s">
+      <c r="H1" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="J1" s="69" t="s">
-        <v>176</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="107" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="M1" s="18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:13" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -1901,19 +1927,16 @@
       <c r="I2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="10"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="M2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1921,1003 +1944,913 @@
         <v>1</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="H3" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="98" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="86" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="87" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="61"/>
-      <c r="L3" s="22" t="s">
+      <c r="J3" s="60"/>
+      <c r="K3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="66">
+      <c r="L3" s="65">
         <v>1</v>
       </c>
-      <c r="N3" s="66">
+      <c r="M3" s="65">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="23">
         <v>2</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="I4" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="J4" s="76" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="M4" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="N4" s="27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D4" s="89" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" s="68"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="L4" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="27" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="23">
         <v>3</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="H5" s="71" t="s">
         <v>153</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="J5" s="76" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="M5" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D5" s="89" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="68"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="L5" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="23">
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G6" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="H6" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="89" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" s="68" t="s">
         <v>6</v>
       </c>
       <c r="I6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="76" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6" s="28"/>
-      <c r="L6" s="26" t="s">
+      <c r="J6" s="28"/>
+      <c r="K6" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="M6" s="63"/>
-      <c r="N6" s="27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L6" s="62"/>
+      <c r="M6" s="27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="23">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G7" s="70"/>
-      <c r="H7" s="71" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" s="89" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="67"/>
+      <c r="H7" s="68" t="s">
         <v>6</v>
       </c>
       <c r="I7" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="76"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="65">
+      <c r="J7" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="26"/>
+      <c r="L7" s="64">
         <v>2</v>
       </c>
-      <c r="N7" s="27"/>
-    </row>
-    <row r="8" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M7" s="27"/>
+    </row>
+    <row r="8" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="23" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="H8" s="71"/>
+        <v>154</v>
+      </c>
+      <c r="D8" s="89" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" s="68"/>
       <c r="I8" s="25"/>
-      <c r="J8" s="76" t="s">
-        <v>6</v>
-      </c>
-      <c r="K8" s="28"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="65">
+      <c r="J8" s="28"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="64">
         <v>1</v>
       </c>
-      <c r="N8" s="27"/>
-    </row>
-    <row r="9" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M8" s="27"/>
+    </row>
+    <row r="9" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="23" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G9" s="70"/>
-      <c r="H9" s="71" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="89" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="67"/>
+      <c r="H9" s="68" t="s">
         <v>6</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="76"/>
-      <c r="K9" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="L9" s="26"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="27"/>
-    </row>
-    <row r="10" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J9" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="26"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="27"/>
+    </row>
+    <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="23" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G10" s="70"/>
-      <c r="H10" s="71" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="89" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" s="67"/>
+      <c r="H10" s="68" t="s">
         <v>6</v>
       </c>
       <c r="I10" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="76"/>
-      <c r="K10" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="L10" s="26"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="27"/>
-    </row>
-    <row r="11" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J10" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="26"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="27"/>
+    </row>
+    <row r="11" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="23" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="H11" s="71"/>
+        <v>155</v>
+      </c>
+      <c r="D11" s="89" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="26"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="68"/>
       <c r="I11" s="25"/>
-      <c r="J11" s="76" t="s">
-        <v>152</v>
-      </c>
-      <c r="K11" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="L11" s="26"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="27"/>
-    </row>
-    <row r="12" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J11" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="K11" s="26"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="27"/>
+    </row>
+    <row r="12" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="94" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G12" s="70" t="s">
-        <v>6</v>
-      </c>
-      <c r="H12" s="71"/>
+      <c r="C12" s="84" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="90" t="s">
+        <v>140</v>
+      </c>
+      <c r="E12" s="26"/>
+      <c r="F12" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="68"/>
       <c r="I12" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="J12" s="76" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="L12" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="M12" s="63"/>
-      <c r="N12" s="27"/>
-    </row>
-    <row r="13" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.5">
+        <v>146</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="L12" s="62"/>
+      <c r="M12" s="27"/>
+    </row>
+    <row r="13" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B13" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="96" t="s">
-        <v>167</v>
-      </c>
-      <c r="G13" s="70"/>
-      <c r="H13" s="71" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="89" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="95" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="67"/>
+      <c r="H13" s="68" t="s">
         <v>6</v>
       </c>
       <c r="I13" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="76"/>
-      <c r="K13" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="L13" s="26"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="27"/>
-    </row>
-    <row r="14" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="J13" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="26"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="27"/>
+    </row>
+    <row r="14" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B14" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="96" t="s">
-        <v>168</v>
-      </c>
-      <c r="G14" s="70"/>
-      <c r="H14" s="71" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="89" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="95" t="s">
+        <v>142</v>
+      </c>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68" t="s">
         <v>6</v>
       </c>
       <c r="I14" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J14" s="76"/>
-      <c r="K14" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="L14" s="26"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="27"/>
-    </row>
-    <row r="15" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J14" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="26"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="27"/>
+    </row>
+    <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="23" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="H15" s="71"/>
+      <c r="D15" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="26"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H15" s="68"/>
       <c r="I15" s="25"/>
-      <c r="J15" s="76" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" s="28"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="68" t="s">
-        <v>151</v>
-      </c>
-      <c r="N15" s="68" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J15" s="28"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="66" t="s">
+        <v>133</v>
+      </c>
+      <c r="M15" s="66" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="23" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="70" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" s="71"/>
+        <v>165</v>
+      </c>
+      <c r="D16" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="26"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="68"/>
       <c r="I16" s="25"/>
-      <c r="J16" s="76" t="s">
-        <v>6</v>
-      </c>
-      <c r="K16" s="28"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="68" t="s">
-        <v>151</v>
-      </c>
-      <c r="N16" s="68" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J16" s="28"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="66" t="s">
+        <v>133</v>
+      </c>
+      <c r="M16" s="66" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G17" s="70"/>
-      <c r="H17" s="71" t="s">
-        <v>152</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J17" s="76"/>
-      <c r="K17" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="L17" s="26"/>
-      <c r="M17" s="63"/>
-      <c r="N17" s="27"/>
-    </row>
-    <row r="18" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+        <v>192</v>
+      </c>
+      <c r="D17" s="89" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="67"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="K17" s="26"/>
+      <c r="L17" s="62"/>
+      <c r="M17" s="27"/>
+    </row>
+    <row r="18" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="23" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="71"/>
+        <v>156</v>
+      </c>
+      <c r="D18" s="89" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="68"/>
       <c r="I18" s="25"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="77" t="s">
-        <v>155</v>
-      </c>
-      <c r="L18" s="26"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="27"/>
-    </row>
-    <row r="19" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J18" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="K18" s="26"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="27"/>
+    </row>
+    <row r="19" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="23" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="D19" s="67" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G19" s="70"/>
-      <c r="H19" s="71" t="s">
-        <v>152</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="J19" s="76"/>
-      <c r="K19" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="L19" s="26"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="27"/>
-    </row>
-    <row r="20" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+        <v>157</v>
+      </c>
+      <c r="D19" s="91" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="67"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="26"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="27"/>
+    </row>
+    <row r="20" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G20" s="70"/>
-      <c r="H20" s="71" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="89" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" s="67"/>
+      <c r="H20" s="68" t="s">
         <v>6</v>
       </c>
       <c r="I20" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J20" s="76"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="27"/>
-    </row>
-    <row r="21" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J20" s="28"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="27"/>
+    </row>
+    <row r="21" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="70"/>
-      <c r="H21" s="71"/>
+        <v>159</v>
+      </c>
+      <c r="D21" s="89" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="26"/>
+      <c r="F21" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G21" s="67"/>
+      <c r="H21" s="68"/>
       <c r="I21" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J21" s="76"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="27"/>
-    </row>
-    <row r="22" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J21" s="28"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="27"/>
+    </row>
+    <row r="22" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G22" s="70"/>
-      <c r="H22" s="71"/>
+        <v>160</v>
+      </c>
+      <c r="D22" s="89" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="26"/>
+      <c r="F22" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="67"/>
+      <c r="H22" s="68"/>
       <c r="I22" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J22" s="76"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="27"/>
-    </row>
-    <row r="23" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J22" s="28"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="27"/>
+    </row>
+    <row r="23" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F23" s="25"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="71" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="89" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" s="64"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="68" t="s">
         <v>6</v>
       </c>
       <c r="I23" s="25"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="M23" s="63"/>
-      <c r="N23" s="27"/>
-    </row>
-    <row r="24" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="J23" s="28"/>
+      <c r="K23" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="L23" s="62"/>
+      <c r="M23" s="27"/>
+    </row>
+    <row r="24" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B24" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="92" t="s">
         <v>171</v>
       </c>
-      <c r="D24" s="98" t="s">
-        <v>173</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F24" s="96" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" s="70" t="s">
-        <v>6</v>
-      </c>
-      <c r="H24" s="71" t="s">
-        <v>175</v>
+      <c r="E24" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F24" s="95" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>146</v>
       </c>
       <c r="I24" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J24" s="76"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="M24" s="63"/>
-      <c r="N24" s="27"/>
-    </row>
-    <row r="25" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J24" s="28"/>
+      <c r="K24" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="L24" s="62"/>
+      <c r="M24" s="27"/>
+    </row>
+    <row r="25" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="D25" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="H25" s="71"/>
+        <v>162</v>
+      </c>
+      <c r="D25" s="91" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="26"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="68"/>
       <c r="I25" s="25"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="63"/>
-      <c r="N25" s="27"/>
-    </row>
-    <row r="26" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J25" s="28"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="62"/>
+      <c r="M25" s="27"/>
+    </row>
+    <row r="26" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="23" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="D26" s="99" t="s">
-        <v>156</v>
-      </c>
-      <c r="E26" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" s="93" t="s">
         <v>136</v>
       </c>
-      <c r="F26" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="71"/>
+      <c r="E26" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="67"/>
+      <c r="H26" s="68"/>
       <c r="I26" s="25"/>
-      <c r="J26" s="76"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="M26" s="63"/>
-      <c r="N26" s="27"/>
-    </row>
-    <row r="27" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J26" s="28"/>
+      <c r="K26" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="62"/>
+      <c r="M26" s="27"/>
+    </row>
+    <row r="27" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="29" t="s">
         <v>22</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E27" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D27" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="F27" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="71"/>
+      <c r="E27" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="67"/>
+      <c r="H27" s="68"/>
       <c r="I27" s="25"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="M27" s="63"/>
-      <c r="N27" s="27"/>
-    </row>
-    <row r="28" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J27" s="28"/>
+      <c r="K27" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="L27" s="62"/>
+      <c r="M27" s="27"/>
+    </row>
+    <row r="28" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="29" t="s">
         <v>23</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E28" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G28" s="70"/>
-      <c r="H28" s="71"/>
+      <c r="E28" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="67"/>
+      <c r="H28" s="68"/>
       <c r="I28" s="25"/>
-      <c r="J28" s="76"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="M28" s="63"/>
-      <c r="N28" s="27"/>
-    </row>
-    <row r="29" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J28" s="28"/>
+      <c r="K28" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="L28" s="62"/>
+      <c r="M28" s="27"/>
+    </row>
+    <row r="29" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="D29" s="67" t="s">
-        <v>146</v>
-      </c>
-      <c r="E29" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="F29" s="31" t="s">
-        <v>136</v>
+        <v>157</v>
+      </c>
+      <c r="D29" s="91" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="96" t="s">
+        <v>125</v>
       </c>
       <c r="G29" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="H29" s="78" t="s">
+      <c r="H29" s="72" t="s">
         <v>6</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="J29" s="33"/>
-      <c r="K29" s="73"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="35"/>
-    </row>
-    <row r="30" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+      <c r="J29" s="70"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="63"/>
+      <c r="M29" s="34"/>
+    </row>
+    <row r="30" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="29" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="D30" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="H30" s="71" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="91" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" s="33"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H30" s="68" t="s">
         <v>6</v>
       </c>
       <c r="I30" s="31"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="63"/>
-      <c r="N30" s="27"/>
-    </row>
-    <row r="31" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J30" s="70"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="27"/>
+    </row>
+    <row r="31" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="29" t="s">
         <v>26</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="D31" s="98" t="s">
-        <v>174</v>
-      </c>
-      <c r="E31" s="31"/>
-      <c r="F31" s="65" t="s">
-        <v>179</v>
+        <v>144</v>
+      </c>
+      <c r="D31" s="92" t="s">
+        <v>172</v>
+      </c>
+      <c r="E31" s="33"/>
+      <c r="F31" s="64" t="s">
+        <v>147</v>
       </c>
       <c r="G31" s="32"/>
-      <c r="H31" s="72"/>
+      <c r="H31" s="69"/>
       <c r="I31" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="J31" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="K31" s="73"/>
-      <c r="L31" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="M31" s="63"/>
-      <c r="N31" s="27"/>
-    </row>
-    <row r="32" spans="2:14" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="J31" s="70"/>
+      <c r="K31" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="L31" s="62"/>
+      <c r="M31" s="27"/>
+    </row>
+    <row r="32" spans="2:13" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B32" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="91" t="s">
-        <v>182</v>
-      </c>
-      <c r="D32" s="100" t="s">
-        <v>183</v>
-      </c>
-      <c r="E32" s="80" t="s">
-        <v>136</v>
-      </c>
-      <c r="F32" s="80"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="I32" s="80"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="M32" s="84"/>
-      <c r="N32" s="85"/>
-    </row>
-    <row r="33" spans="2:14" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="86" t="s">
-        <v>158</v>
-      </c>
-      <c r="C33" s="87"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88">
+      <c r="C32" s="82" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="94" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="99" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="97"/>
+      <c r="G32" s="100"/>
+      <c r="H32" s="96" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" s="74"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="76" t="s">
+        <v>123</v>
+      </c>
+      <c r="L32" s="77"/>
+      <c r="M32" s="78"/>
+    </row>
+    <row r="33" spans="2:13" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B33" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="79"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="104">
         <f>COUNTIF(E3:E32, "Y")</f>
-        <v>16</v>
-      </c>
-      <c r="F33" s="88">
+        <v>15</v>
+      </c>
+      <c r="F33" s="80">
         <f>COUNTIF(F3:F32, "Y")</f>
-        <v>16</v>
-      </c>
-      <c r="G33" s="88">
+        <v>15</v>
+      </c>
+      <c r="G33" s="105">
         <f>COUNTIF(G3:G32, "Y")</f>
         <v>9</v>
       </c>
-      <c r="H33" s="88" t="s">
-        <v>180</v>
-      </c>
-      <c r="I33" s="88" t="s">
-        <v>181</v>
-      </c>
-      <c r="J33" s="88" t="s">
-        <v>159</v>
-      </c>
-      <c r="K33" s="88" t="s">
-        <v>6</v>
-      </c>
-      <c r="L33" s="89">
-        <f>COUNTA(L3:L32)</f>
+      <c r="H33" s="102" t="s">
+        <v>148</v>
+      </c>
+      <c r="I33" s="80" t="s">
+        <v>149</v>
+      </c>
+      <c r="J33" s="103" t="s">
+        <v>6</v>
+      </c>
+      <c r="K33" s="106">
+        <f>COUNTA(K3:K32)</f>
         <v>12</v>
       </c>
-      <c r="M33" s="90"/>
-      <c r="N33" s="92"/>
-    </row>
-    <row r="34" spans="2:14" ht="19" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="L33" s="81"/>
+      <c r="M33" s="83"/>
+    </row>
+    <row r="34" spans="2:13" ht="19" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B34" s="1"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
       <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-    </row>
-    <row r="35" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B35" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C35" s="94" t="s">
-        <v>169</v>
-      </c>
-      <c r="D35" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
+    </row>
+    <row r="35" spans="2:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="C36" s="93" t="s">
-        <v>162</v>
-      </c>
-      <c r="D36" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-    </row>
-    <row r="37" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="C37" s="93" t="s">
-        <v>163</v>
-      </c>
-      <c r="D37" s="95" t="s">
-        <v>165</v>
-      </c>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-    </row>
-    <row r="38" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-    </row>
-    <row r="39" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-    </row>
-    <row r="40" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-    </row>
-    <row r="41" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
+    </row>
+    <row r="36" spans="2:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+    </row>
+    <row r="37" spans="2:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+    </row>
+    <row r="38" spans="2:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+    </row>
+    <row r="39" spans="2:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+    </row>
+    <row r="40" spans="2:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+    </row>
+    <row r="41" spans="2:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
@@ -2933,7 +2866,7 @@
   <cols>
     <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="44.7265625" bestFit="1" customWidth="1"/>
@@ -2963,549 +2896,547 @@
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>43</v>
       </c>
       <c r="F2" s="10"/>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="54" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="19" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="51">
+        <v>2</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B4" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="41">
+        <v>3</v>
+      </c>
+      <c r="F4" s="39"/>
+      <c r="G4" s="40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B5" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="41">
+        <v>3</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B6" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="41">
+        <v>3</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B7" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="41">
+        <v>2</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="53" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B8" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="41">
+        <v>2</v>
+      </c>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B9" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="41">
+        <v>1</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="41">
+        <v>3</v>
+      </c>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
+    </row>
+    <row r="11" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B11" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="41">
+        <v>3</v>
+      </c>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40"/>
+    </row>
+    <row r="12" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B12" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="41">
+        <v>3</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="40"/>
+    </row>
+    <row r="13" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B13" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="41">
+        <v>3</v>
+      </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B14" s="57" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="41">
+        <v>1</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B15" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15" s="108" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="41">
+        <v>1</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B16" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="38" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="19" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="57" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="52">
+      <c r="D16" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="41">
+        <v>1</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B17" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="41">
+        <v>1</v>
+      </c>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B18" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="41">
         <v>2</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F18" s="39"/>
+      <c r="G18" s="40"/>
+    </row>
+    <row r="19" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B19" s="57">
+        <v>47</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="41">
+        <v>2</v>
+      </c>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B20" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="41">
+        <v>1</v>
+      </c>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B21" s="57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="41">
+        <v>1</v>
+      </c>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B22" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" s="41">
+        <v>2</v>
+      </c>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B23" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="41">
+        <v>2</v>
+      </c>
+      <c r="F23" s="39"/>
+      <c r="G23" s="53" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B24" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="41">
+        <v>2</v>
+      </c>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
+    </row>
+    <row r="25" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B25" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="41">
+        <v>2</v>
+      </c>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
+    </row>
+    <row r="26" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B26" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="41">
+        <v>3</v>
+      </c>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40"/>
+    </row>
+    <row r="27" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B27" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="43">
+        <v>1</v>
+      </c>
+      <c r="F27" s="44"/>
+      <c r="G27" s="40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B28" s="58" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="43">
+        <v>1</v>
+      </c>
+      <c r="F28" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="53" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="42">
+      <c r="G28" s="40"/>
+    </row>
+    <row r="29" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B29" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="43">
+        <v>2</v>
+      </c>
+      <c r="F29" s="44"/>
+      <c r="G29" s="45"/>
+    </row>
+    <row r="30" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B30" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="108" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="43">
         <v>3</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B5" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="42">
+      <c r="F30" s="44"/>
+      <c r="G30" s="40"/>
+    </row>
+    <row r="31" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B31" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="D31" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="E31" s="41">
         <v>3</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B6" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="42">
-        <v>3</v>
-      </c>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B7" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="42">
-        <v>2</v>
-      </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="54" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="42">
-        <v>2</v>
-      </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B9" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="42">
-        <v>1</v>
-      </c>
-      <c r="F9" s="40" t="s">
+      <c r="F31" s="39"/>
+      <c r="G31" s="53" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B32" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="48">
+        <v>4</v>
+      </c>
+      <c r="F32" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="54" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" s="42">
-        <v>3</v>
-      </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-    </row>
-    <row r="11" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B11" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="42">
-        <v>3</v>
-      </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-    </row>
-    <row r="12" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B12" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="42">
-        <v>1</v>
-      </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
-    </row>
-    <row r="13" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B13" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="42">
-        <v>1</v>
-      </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B14" s="58" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="42">
-        <v>1</v>
-      </c>
-      <c r="F14" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="41" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B15" s="58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="42">
-        <v>1</v>
-      </c>
-      <c r="F15" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="41" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="42">
-        <v>1</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="42">
-        <v>1</v>
-      </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B18" s="58" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="42">
-        <v>2</v>
-      </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
-    </row>
-    <row r="19" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B19" s="58">
-        <v>47</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E19" s="42">
-        <v>2</v>
-      </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B20" s="58" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="42">
-        <v>1</v>
-      </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B21" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="42">
-        <v>1</v>
-      </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B22" s="58" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="42">
-        <v>2</v>
-      </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B23" s="58" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="42">
-        <v>2</v>
-      </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="54" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B24" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" s="42">
-        <v>2</v>
-      </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
-    </row>
-    <row r="25" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B25" s="58" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" s="42">
-        <v>2</v>
-      </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
-    </row>
-    <row r="26" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B26" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="42">
-        <v>3</v>
-      </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
-    </row>
-    <row r="27" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B27" s="59" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="E27" s="44">
-        <v>1</v>
-      </c>
-      <c r="F27" s="45"/>
-      <c r="G27" s="41" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B28" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" s="44">
-        <v>1</v>
-      </c>
-      <c r="F28" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="41"/>
-    </row>
-    <row r="29" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B29" s="59" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="44">
-        <v>2</v>
-      </c>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46"/>
-    </row>
-    <row r="30" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B30" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" s="44">
-        <v>3</v>
-      </c>
-      <c r="F30" s="45"/>
-      <c r="G30" s="41"/>
-    </row>
-    <row r="31" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B31" s="59" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="E31" s="42">
-        <v>3</v>
-      </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="54" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="19" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="60" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="E32" s="49">
-        <v>4</v>
-      </c>
-      <c r="F32" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="51"/>
+      <c r="G32" s="50"/>
     </row>
     <row r="33" spans="5:5" ht="19" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="E33" s="56"/>
+      <c r="E33" s="55"/>
     </row>
     <row r="34" spans="5:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="E34" s="56"/>
+      <c r="E34" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rules/Card Manifest.xlsx
+++ b/rules/Card Manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\States of Siege Diriyah\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9582C6BF-9963-43D7-B861-575EB6DE7EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89833AE-10CF-4E73-AE3A-63F8455DDEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,9 +364,6 @@
     <t>Najd Interdiction</t>
   </si>
   <si>
-    <t>Remove 2 Ottoman Units</t>
-  </si>
-  <si>
     <t>Tribal Raids on Supply Lines</t>
   </si>
   <si>
@@ -415,21 +412,9 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Place Local Traitors marker on S Front Wahhabi Space</t>
-  </si>
-  <si>
     <t>Add 1 Artillery, 1 Cavalry to Siege Camp</t>
   </si>
   <si>
-    <t>-2 Wahhabi Morale</t>
-  </si>
-  <si>
-    <t>No Wahhabi Events or Actions this turn</t>
-  </si>
-  <si>
-    <t>Remove one Wahhabi Artillery Unit</t>
-  </si>
-  <si>
     <t>Supply Status to NORMAL</t>
   </si>
   <si>
@@ -472,9 +457,6 @@
     <t>REDEPLOYMENT</t>
   </si>
   <si>
-    <t>-2 Wahhabi Supply; no Wahhabi Actions this turn</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -556,9 +538,6 @@
     <t>Redeploy 2 artillery, 2 cavalry from siege camp to slowest advance</t>
   </si>
   <si>
-    <t>-1 Wahhabi Supply; no Wahhabi Actions this turn</t>
-  </si>
-  <si>
     <t>Add Elite Cavalry to W and NE Fronts unless outnumbered in Supply Lines</t>
   </si>
   <si>
@@ -568,9 +547,6 @@
     <t>RAPID ADVANCE</t>
   </si>
   <si>
-    <t>Automatic advance into the next Settlement, Wadi or Heights space</t>
-  </si>
-  <si>
     <t xml:space="preserve">TACTICAL </t>
   </si>
   <si>
@@ -583,12 +559,6 @@
     <t>All Units in Suppy Lines Attackers box to Reserve</t>
   </si>
   <si>
-    <t>CAVALRY DESERTION</t>
-  </si>
-  <si>
-    <t>Remove one Wahhabi Khayala Unit</t>
-  </si>
-  <si>
     <t>Cavalry Dispersed</t>
   </si>
   <si>
@@ -614,6 +584,36 @@
   </si>
   <si>
     <t>ARTILLERY ATTRITION</t>
+  </si>
+  <si>
+    <t>Remove 1 Cavaly and 1 Artillery Ottoman Unit</t>
+  </si>
+  <si>
+    <t>Automatic advance into the next space</t>
+  </si>
+  <si>
+    <t>Place Local Traitors marker on S Front Saudi Space</t>
+  </si>
+  <si>
+    <t>Remove one Saudi Artillery Unit</t>
+  </si>
+  <si>
+    <t>-2 Saudi Morale</t>
+  </si>
+  <si>
+    <t>No Saudi Events or Actions this turn</t>
+  </si>
+  <si>
+    <t>-2 Saudi Supply; no Saudi Actions this turn</t>
+  </si>
+  <si>
+    <t>-1 Saudi Supply; no Saudi Actions this turn</t>
+  </si>
+  <si>
+    <t>ARTILLERY RESUPPLY</t>
+  </si>
+  <si>
+    <t>Move Artillery Units from  Siege Camp to North-Eastern Front</t>
   </si>
 </sst>
 </file>
@@ -1492,9 +1492,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1541,6 +1538,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1890,13 +1888,13 @@
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="I1" s="107" t="s">
-        <v>179</v>
+        <v>170</v>
+      </c>
+      <c r="I1" s="106" t="s">
+        <v>171</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>29</v>
@@ -1944,19 +1942,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D3" s="88" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" s="98" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="97" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="65" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="86" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H3" s="87" t="s">
         <v>6</v>
@@ -1980,19 +1978,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D4" s="89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F4" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G4" s="67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="25"/>
@@ -2000,13 +1998,13 @@
         <v>6</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L4" s="62" t="s">
         <v>6</v>
       </c>
       <c r="M4" s="27" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -2014,19 +2012,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D5" s="89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G5" s="67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H5" s="68"/>
       <c r="I5" s="25"/>
@@ -2034,13 +2032,13 @@
         <v>6</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L5" s="62" t="s">
         <v>6</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -2048,19 +2046,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H6" s="68" t="s">
         <v>6</v>
@@ -2074,7 +2072,7 @@
       </c>
       <c r="L6" s="62"/>
       <c r="M6" s="27" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -2082,16 +2080,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D7" s="89" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F7" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G7" s="67"/>
       <c r="H7" s="68" t="s">
@@ -2114,15 +2112,15 @@
         <v>2</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D8" s="89" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="64"/>
       <c r="G8" s="67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H8" s="68"/>
       <c r="I8" s="25"/>
@@ -2138,13 +2136,13 @@
         <v>3</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D9" s="89" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F9" s="64" t="s">
         <v>6</v>
@@ -2168,16 +2166,16 @@
         <v>4</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D10" s="89" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G10" s="67"/>
       <c r="H10" s="68" t="s">
@@ -2198,20 +2196,20 @@
         <v>5</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D11" s="89" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="64"/>
       <c r="G11" s="67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H11" s="68"/>
       <c r="I11" s="25"/>
       <c r="J11" s="28" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="K11" s="26"/>
       <c r="L11" s="62"/>
@@ -2222,27 +2220,27 @@
         <v>7</v>
       </c>
       <c r="C12" s="84" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D12" s="90" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E12" s="26"/>
       <c r="F12" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="H12" s="68"/>
       <c r="I12" s="25" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J12" s="28" t="s">
         <v>6</v>
       </c>
       <c r="K12" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L12" s="62"/>
       <c r="M12" s="27"/>
@@ -2252,16 +2250,16 @@
         <v>8</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D13" s="89" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="95" t="s">
-        <v>141</v>
+      <c r="F13" s="94" t="s">
+        <v>136</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="68" t="s">
@@ -2282,16 +2280,16 @@
         <v>9</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D14" s="89" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="95" t="s">
-        <v>142</v>
+      <c r="F14" s="94" t="s">
+        <v>137</v>
       </c>
       <c r="G14" s="67"/>
       <c r="H14" s="68" t="s">
@@ -2315,22 +2313,22 @@
         <v>34</v>
       </c>
       <c r="D15" s="89" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E15" s="26"/>
       <c r="F15" s="64"/>
       <c r="G15" s="67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H15" s="68"/>
       <c r="I15" s="25"/>
       <c r="J15" s="28"/>
       <c r="K15" s="26"/>
       <c r="L15" s="66" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="M15" s="66" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -2338,10 +2336,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D16" s="89" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E16" s="26"/>
       <c r="F16" s="64"/>
@@ -2353,10 +2351,10 @@
       <c r="J16" s="28"/>
       <c r="K16" s="26"/>
       <c r="L16" s="66" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="M16" s="66" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
@@ -2364,22 +2362,22 @@
         <v>11</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D17" s="89" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F17" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G17" s="67"/>
       <c r="H17" s="68"/>
       <c r="I17" s="25"/>
       <c r="J17" s="28" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K17" s="26"/>
       <c r="L17" s="62"/>
@@ -2390,10 +2388,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D18" s="89" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E18" s="26"/>
       <c r="F18" s="64"/>
@@ -2401,7 +2399,7 @@
       <c r="H18" s="68"/>
       <c r="I18" s="25"/>
       <c r="J18" s="71" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K18" s="26"/>
       <c r="L18" s="62"/>
@@ -2412,16 +2410,16 @@
         <v>14</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D19" s="91" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F19" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G19" s="67"/>
       <c r="H19" s="68"/>
@@ -2438,16 +2436,16 @@
         <v>15</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D20" s="89" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F20" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G20" s="67"/>
       <c r="H20" s="68" t="s">
@@ -2466,14 +2464,14 @@
         <v>16</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D21" s="89" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="E21" s="26"/>
       <c r="F21" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G21" s="67"/>
       <c r="H21" s="68"/>
@@ -2490,14 +2488,14 @@
         <v>17</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D22" s="89" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E22" s="26"/>
       <c r="F22" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G22" s="67"/>
       <c r="H22" s="68"/>
@@ -2514,13 +2512,13 @@
         <v>19</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D23" s="89" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F23" s="64"/>
       <c r="G23" s="67"/>
@@ -2530,7 +2528,7 @@
       <c r="I23" s="25"/>
       <c r="J23" s="28"/>
       <c r="K23" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L23" s="62"/>
       <c r="M23" s="27"/>
@@ -2540,29 +2538,29 @@
         <v>18</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="92" t="s">
-        <v>171</v>
+        <v>139</v>
+      </c>
+      <c r="D24" s="90" t="s">
+        <v>165</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="F24" s="95" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" s="94" t="s">
         <v>6</v>
       </c>
       <c r="G24" s="67" t="s">
         <v>6</v>
       </c>
       <c r="H24" s="68" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I24" s="25" t="s">
         <v>6</v>
       </c>
       <c r="J24" s="28"/>
       <c r="K24" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L24" s="62"/>
       <c r="M24" s="27"/>
@@ -2572,15 +2570,15 @@
         <v>20</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D25" s="91" t="s">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="E25" s="26"/>
       <c r="F25" s="64"/>
       <c r="G25" s="67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H25" s="68"/>
       <c r="I25" s="25"/>
@@ -2594,23 +2592,23 @@
         <v>21</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="D26" s="93" t="s">
-        <v>136</v>
+        <v>157</v>
+      </c>
+      <c r="D26" s="92" t="s">
+        <v>131</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="68"/>
       <c r="I26" s="25"/>
       <c r="J26" s="28"/>
       <c r="K26" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L26" s="62"/>
       <c r="M26" s="27"/>
@@ -2620,23 +2618,23 @@
         <v>22</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D27" s="89" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F27" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G27" s="67"/>
       <c r="H27" s="68"/>
       <c r="I27" s="25"/>
       <c r="J27" s="28"/>
       <c r="K27" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L27" s="62"/>
       <c r="M27" s="27"/>
@@ -2646,23 +2644,23 @@
         <v>23</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D28" s="89" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F28" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G28" s="67"/>
       <c r="H28" s="68"/>
       <c r="I28" s="25"/>
       <c r="J28" s="28"/>
       <c r="K28" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L28" s="62"/>
       <c r="M28" s="27"/>
@@ -2672,16 +2670,16 @@
         <v>25</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D29" s="91" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="F29" s="96" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="F29" s="95" t="s">
+        <v>124</v>
       </c>
       <c r="G29" s="32" t="s">
         <v>6</v>
@@ -2702,15 +2700,15 @@
         <v>24</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D30" s="91" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E30" s="33"/>
-      <c r="F30" s="96"/>
+      <c r="F30" s="95"/>
       <c r="G30" s="67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H30" s="68" t="s">
         <v>6</v>
@@ -2726,23 +2724,23 @@
         <v>26</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="92" t="s">
-        <v>172</v>
+        <v>139</v>
+      </c>
+      <c r="D31" s="90" t="s">
+        <v>166</v>
       </c>
       <c r="E31" s="33"/>
       <c r="F31" s="64" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G31" s="32"/>
       <c r="H31" s="69"/>
       <c r="I31" s="31" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J31" s="70"/>
       <c r="K31" s="33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L31" s="62"/>
       <c r="M31" s="27"/>
@@ -2752,34 +2750,34 @@
         <v>27</v>
       </c>
       <c r="C32" s="82" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" s="94" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="99" t="s">
-        <v>125</v>
-      </c>
-      <c r="F32" s="97"/>
-      <c r="G32" s="100"/>
-      <c r="H32" s="96" t="s">
-        <v>146</v>
+        <v>144</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" s="98" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="96"/>
+      <c r="G32" s="99"/>
+      <c r="H32" s="95" t="s">
+        <v>140</v>
       </c>
       <c r="I32" s="74"/>
       <c r="J32" s="75"/>
       <c r="K32" s="76" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L32" s="77"/>
       <c r="M32" s="78"/>
     </row>
     <row r="33" spans="2:13" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B33" s="85" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C33" s="79"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="104">
+      <c r="D33" s="100"/>
+      <c r="E33" s="103">
         <f>COUNTIF(E3:E32, "Y")</f>
         <v>15</v>
       </c>
@@ -2787,20 +2785,20 @@
         <f>COUNTIF(F3:F32, "Y")</f>
         <v>15</v>
       </c>
-      <c r="G33" s="105">
+      <c r="G33" s="104">
         <f>COUNTIF(G3:G32, "Y")</f>
         <v>9</v>
       </c>
-      <c r="H33" s="102" t="s">
-        <v>148</v>
+      <c r="H33" s="101" t="s">
+        <v>142</v>
       </c>
       <c r="I33" s="80" t="s">
-        <v>149</v>
-      </c>
-      <c r="J33" s="103" t="s">
-        <v>6</v>
-      </c>
-      <c r="K33" s="106">
+        <v>143</v>
+      </c>
+      <c r="J33" s="102" t="s">
+        <v>6</v>
+      </c>
+      <c r="K33" s="105">
         <f>COUNTA(K3:K32)</f>
         <v>12</v>
       </c>
@@ -3041,7 +3039,7 @@
       <c r="C10" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="108" t="s">
         <v>88</v>
       </c>
       <c r="E10" s="41">
@@ -3057,7 +3055,7 @@
       <c r="C11" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="108" t="s">
         <v>88</v>
       </c>
       <c r="E11" s="41">
@@ -3074,7 +3072,7 @@
         <v>90</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="E12" s="41">
         <v>3</v>
@@ -3125,10 +3123,10 @@
         <v>63</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="D15" s="108" t="s">
-        <v>188</v>
+        <v>176</v>
+      </c>
+      <c r="D15" s="107" t="s">
+        <v>178</v>
       </c>
       <c r="E15" s="41">
         <v>1</v>
@@ -3179,10 +3177,10 @@
         <v>66</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D18" s="42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E18" s="41">
         <v>2</v>
@@ -3249,10 +3247,10 @@
         <v>69</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E22" s="41">
         <v>2</v>
@@ -3267,10 +3265,10 @@
         <v>70</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E23" s="41">
         <v>2</v>
@@ -3320,7 +3318,7 @@
         <v>108</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="E26" s="41">
         <v>3</v>
@@ -3333,17 +3331,17 @@
         <v>74</v>
       </c>
       <c r="C27" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="42" t="s">
         <v>110</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>111</v>
       </c>
       <c r="E27" s="43">
         <v>1</v>
       </c>
       <c r="F27" s="44"/>
       <c r="G27" s="40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
@@ -3351,10 +3349,10 @@
         <v>75</v>
       </c>
       <c r="C28" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="42" t="s">
         <v>113</v>
-      </c>
-      <c r="D28" s="42" t="s">
-        <v>114</v>
       </c>
       <c r="E28" s="43">
         <v>1</v>
@@ -3369,10 +3367,10 @@
         <v>76</v>
       </c>
       <c r="C29" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="107" t="s">
         <v>115</v>
-      </c>
-      <c r="D29" s="42" t="s">
-        <v>116</v>
       </c>
       <c r="E29" s="43">
         <v>2</v>
@@ -3385,10 +3383,10 @@
         <v>77</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" s="108" t="s">
-        <v>188</v>
+        <v>116</v>
+      </c>
+      <c r="D30" s="107" t="s">
+        <v>178</v>
       </c>
       <c r="E30" s="43">
         <v>3</v>
@@ -3401,10 +3399,10 @@
         <v>78</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E31" s="41">
         <v>3</v>
@@ -3419,10 +3417,10 @@
         <v>79</v>
       </c>
       <c r="C32" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="47" t="s">
         <v>119</v>
-      </c>
-      <c r="D32" s="47" t="s">
-        <v>120</v>
       </c>
       <c r="E32" s="48">
         <v>4</v>
